--- a/result/bayes_sum/bayes_improvement_summary.xlsx
+++ b/result/bayes_sum/bayes_improvement_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,7 @@
         <v>23.07692307692308</v>
       </c>
       <c r="H3" t="n">
-        <v>49.11819786611584</v>
+        <v>49.11819786611585</v>
       </c>
     </row>
     <row r="4">
@@ -570,7 +570,7 @@
         <v>2.09190853483501</v>
       </c>
       <c r="E5" t="n">
-        <v>4.422874003791364</v>
+        <v>4.422874003791363</v>
       </c>
       <c r="F5" t="n">
         <v>15.99992249476374</v>
